--- a/cuadros/JUNIO/SAN JUAN.xlsx
+++ b/cuadros/JUNIO/SAN JUAN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260604081728</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SAN JUAN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES RUBYMAR R.M C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>009114</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>INGRID D. LOPEZ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>colocaron 12 cesta de 2.2kg y eran 10cesta de 2.2</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_105117_0.png INC_105117_1.png</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260604105117</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/SAN JUAN.xlsx
+++ b/cuadros/JUNIO/SAN JUAN.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +632,71 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260604105117</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SAN JUAN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>03062026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JHONNY J. BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>faltante de cilantro de 80gr por no estar en el documento cancelado por la sucursal</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>COB_075616_0.jpg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ID_20260605075616</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/SAN JUAN.xlsx
+++ b/cuadros/JUNIO/SAN JUAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,6 +697,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>ID_20260605075616</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAN JUAN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>03062026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESUS HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>faltante de hierbabuena por no estar en el documento cancelado por la sucursal</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>COB_080440_0.jpg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>INC_080440_0.jpg</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ID_20260605080440</t>
         </is>
       </c>
     </row>
